--- a/output/graficos_dimensiones/comunal_p_aps_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:38</t>
+    <t xml:space="preserve">2026-09-09 23:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:37</t>
+    <t xml:space="preserve">2026-09-18 10:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:26</t>
+    <t xml:space="preserve">2026-09-23 12:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:59</t>
+    <t xml:space="preserve">2026-10-02 15:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2020_biobio.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Nacimiento</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Hualqui</t>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">San Rosendo</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Chiguayante</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:03</t>
+    <t xml:space="preserve">2026-10-04 09:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:41</t>
+    <t xml:space="preserve">2026-10-05 13:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
